--- a/data/trans_dic/P39A5_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,93; 92,65</t>
+          <t>80,65; 92,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,93; 93,51</t>
+          <t>83,49; 93,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,79; 91,89</t>
+          <t>83,39; 91,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,9; 90,98</t>
+          <t>82,08; 90,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,99; 85,98</t>
+          <t>41,61; 86,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,51; 86,97</t>
+          <t>58,73; 86,73</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,71; 90,85</t>
+          <t>85,06; 90,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,51</t>
+          <t>83,67; 88,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,09</t>
+          <t>85,09; 88,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,28; 96,55</t>
+          <t>87,39; 97,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,24; 87,62</t>
+          <t>83,38; 87,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,15; 94,05</t>
+          <t>86,27; 93,53</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,44; 89,1</t>
+          <t>83,81; 89,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,38; 90,6</t>
+          <t>86,09; 90,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,72; 89,12</t>
+          <t>85,51; 89,16</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,38; 91,11</t>
+          <t>85,52; 91,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,54; 96,77</t>
+          <t>86,5; 96,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,37; 96,1</t>
+          <t>87,34; 95,28</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,6; 86,46</t>
+          <t>78,7; 86,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,26; 85,27</t>
+          <t>79,38; 85,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,25; 84,8</t>
+          <t>80,21; 84,81</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,56; 91,01</t>
+          <t>86,62; 91,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,85; 87,91</t>
+          <t>78,47; 87,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,85; 88,45</t>
+          <t>83,65; 88,57</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>284383; 329644</t>
+          <t>286962; 330851</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>232972; 259563</t>
+          <t>231760; 258833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>530731; 582008</t>
+          <t>528206; 581499</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>318713; 354044</t>
+          <t>319418; 353026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202552; 414707</t>
+          <t>200726; 414869</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518619; 757978</t>
+          <t>511867; 755837</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>432333; 463679</t>
+          <t>434131; 464004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>433766; 458954</t>
+          <t>433858; 458387</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>874797; 916693</t>
+          <t>875506; 914084</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>740034; 818624</t>
+          <t>740984; 822406</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>540179; 568594</t>
+          <t>541091; 567340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1289424; 1407651</t>
+          <t>1291258; 1399952</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>436681; 466296</t>
+          <t>438614; 466687</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>441534; 463143</t>
+          <t>440089; 461146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>886751; 921933</t>
+          <t>884589; 922353</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>286928; 306176</t>
+          <t>287391; 305993</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>491954; 550109</t>
+          <t>491715; 548733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>790274; 869217</t>
+          <t>790019; 861825</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>192224; 211424</t>
+          <t>192454; 211419</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>269492; 289934</t>
+          <t>269903; 290042</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469088; 495729</t>
+          <t>468866; 495786</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2776002; 2918806</t>
+          <t>2778139; 2920246</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2672728; 2942438</t>
+          <t>2626326; 2941614</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5495729; 5797475</t>
+          <t>5482791; 5805045</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A5_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,65; 92,99</t>
+          <t>81,22; 91,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,49; 93,25</t>
+          <t>83,07; 92,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,39; 91,81</t>
+          <t>83,61; 91,31</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,08; 90,72</t>
+          <t>81,87; 90,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,61; 86,01</t>
+          <t>81,71; 88,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,73; 86,73</t>
+          <t>83,24; 88,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,06; 90,92</t>
+          <t>83,61; 89,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,4</t>
+          <t>83,08; 88,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,09; 88,84</t>
+          <t>84,37; 87,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,39; 97,0</t>
+          <t>85,39; 90,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,38; 87,43</t>
+          <t>82,89; 87,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,27; 93,53</t>
+          <t>84,89; 88,05</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,81; 89,17</t>
+          <t>83,06; 88,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,09; 90,21</t>
+          <t>85,57; 89,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,51; 89,16</t>
+          <t>84,95; 88,63</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,52; 91,05</t>
+          <t>85,23; 90,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86,5; 96,53</t>
+          <t>84,74; 89,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,34; 95,28</t>
+          <t>85,74; 89,38</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>83,18%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>82,4%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>82,73%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,7; 86,45</t>
+          <t>78,92; 86,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,38; 85,31</t>
+          <t>79,3; 85,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,21; 84,81</t>
+          <t>80,28; 85,15</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,05</t>
+          <t>85,53; 88,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,47; 87,89</t>
+          <t>84,99; 87,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,57</t>
+          <t>85,56; 87,2</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>311647</t>
+          <t>308916</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>248593</t>
+          <t>287163</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560241</t>
+          <t>596079</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>286962; 330851</t>
+          <t>287346; 325200</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>231760; 258833</t>
+          <t>269118; 299499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>528206; 581499</t>
+          <t>566689; 618863</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>338344</t>
+          <t>380334</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>351237</t>
+          <t>394681</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>689581</t>
+          <t>775015</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319418; 353026</t>
+          <t>358489; 395894</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>200726; 414869</t>
+          <t>376564; 409007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511867; 755837</t>
+          <t>748129; 796975</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>449128</t>
+          <t>500322</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>446984</t>
+          <t>504990</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>896112</t>
+          <t>1005311</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>434131; 464004</t>
+          <t>482531; 516435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>433858; 458387</t>
+          <t>489700; 520407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>875506; 914084</t>
+          <t>984250; 1026466</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>777527</t>
+          <t>572830</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>555484</t>
+          <t>597160</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1333011</t>
+          <t>1169991</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>740984; 822406</t>
+          <t>554979; 587617</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>541091; 567340</t>
+          <t>581294; 610976</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1291258; 1399952</t>
+          <t>1147061; 1189712</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>452308</t>
+          <t>484548</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>451603</t>
+          <t>496549</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>903911</t>
+          <t>981098</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>438614; 466687</t>
+          <t>468328; 499691</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>440089; 461146</t>
+          <t>484824; 507625</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>884589; 922353</t>
+          <t>960306; 1001885</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>297502</t>
+          <t>326220</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>522881</t>
+          <t>347184</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>820382</t>
+          <t>673404</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>287391; 305993</t>
+          <t>315390; 336334</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>491715; 548733</t>
+          <t>336898; 355984</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>790019; 861825</t>
+          <t>658160; 686083</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>202325</t>
+          <t>223569</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>280662</t>
+          <t>306781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>482987</t>
+          <t>530350</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>192454; 211419</t>
+          <t>212107; 233097</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>269903; 290042</t>
+          <t>295241; 317600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>468866; 495786</t>
+          <t>514642; 545846</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2828781</t>
+          <t>2796740</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2857444</t>
+          <t>2934509</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5686225</t>
+          <t>5731249</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2778139; 2920246</t>
+          <t>2755388; 2839553</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2626326; 2941614</t>
+          <t>2899864; 2969986</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5482791; 5805045</t>
+          <t>5675764; 5784167</t>
         </is>
       </c>
     </row>
